--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.27029420582912</v>
+        <v>7.356422808447233</v>
       </c>
       <c r="D2" t="n">
-        <v>39.07486517713848</v>
+        <v>6.349665591285004</v>
       </c>
       <c r="E2" t="n">
-        <v>9.361918442168175</v>
+        <v>1.521311746852328</v>
       </c>
       <c r="F2" t="n">
-        <v>11.67172876162394</v>
+        <v>1.896655923763891</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.68607134589231</v>
+        <v>3.5239865937075</v>
       </c>
       <c r="D3" t="n">
-        <v>22.10551637420246</v>
+        <v>3.5921464108079</v>
       </c>
       <c r="E3" t="n">
-        <v>9.361918442168175</v>
+        <v>1.521311746852328</v>
       </c>
       <c r="F3" t="n">
-        <v>11.67172876162394</v>
+        <v>1.896655923763891</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.59655134894533</v>
+        <v>5.459439594203617</v>
       </c>
       <c r="D4" t="n">
-        <v>45.54482800521582</v>
+        <v>7.401034550847571</v>
       </c>
       <c r="E4" t="n">
-        <v>9.361918442168175</v>
+        <v>1.521311746852328</v>
       </c>
       <c r="F4" t="n">
-        <v>11.67172876162394</v>
+        <v>1.896655923763891</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.53879965436342</v>
+        <v>7.237554943834057</v>
       </c>
       <c r="D5" t="n">
-        <v>12.77905668687269</v>
+        <v>2.076596711616812</v>
       </c>
       <c r="E5" t="n">
-        <v>9.361918442168175</v>
+        <v>1.521311746852328</v>
       </c>
       <c r="F5" t="n">
-        <v>11.67172876162394</v>
+        <v>1.896655923763891</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.59070651669883</v>
+        <v>6.59598980896356</v>
       </c>
       <c r="D6" t="n">
-        <v>47.76269795072584</v>
+        <v>7.761438416992949</v>
       </c>
       <c r="E6" t="n">
-        <v>9.361918442168175</v>
+        <v>1.521311746852328</v>
       </c>
       <c r="F6" t="n">
-        <v>11.67172876162394</v>
+        <v>1.896655923763891</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>52.16981606817013</v>
+        <v>8.477595111077646</v>
       </c>
       <c r="D7" t="n">
-        <v>31.99228162429618</v>
+        <v>5.198745763948128</v>
       </c>
       <c r="E7" t="n">
-        <v>9.361918442168175</v>
+        <v>1.521311746852328</v>
       </c>
       <c r="F7" t="n">
-        <v>11.67172876162394</v>
+        <v>1.896655923763891</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.72138680020321</v>
+        <v>5.317225355033021</v>
       </c>
       <c r="D8" t="n">
-        <v>29.30596630930631</v>
+        <v>4.762219525262276</v>
       </c>
       <c r="E8" t="n">
-        <v>9.361918442168175</v>
+        <v>1.521311746852328</v>
       </c>
       <c r="F8" t="n">
-        <v>11.67172876162394</v>
+        <v>1.896655923763891</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
